--- a/智能箱通用功能统计.xlsx
+++ b/智能箱通用功能统计.xlsx
@@ -637,6 +637,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>① 将故障判断功能放在设备端，使用uint32_t类型（0xFFFFFFFF）故障码来区分，初步分为电源类、网路类、传感器类3种；</t>
     </r>
     <r>
@@ -666,6 +673,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>原因：配置、传感器搜索等JSON上报，平台偶尔接收不全，是由于平台无法判断一包数据是否完整导致的；</t>
     </r>
     <r>
@@ -695,6 +709,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>设备向平台指定地址发送日志文件。</t>
     </r>
     <r>
@@ -751,6 +772,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>1、网络通的情况下，查看经过几个路由点到的机房；</t>
     </r>
     <r>
@@ -777,6 +805,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>根据设备上报的型号进行判断版本，不同的设备使用不同的版本，用于界面展示，</t>
     </r>
     <r>
@@ -836,6 +871,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>通过ping的方式来检测点位台账列表中各个摄像机的在线情况。</t>
     </r>
     <r>
@@ -3891,7 +3933,7 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
-    <col min="2" max="2" width="83.75" customWidth="1"/>
+    <col min="2" max="2" width="34.3416666666667" customWidth="1"/>
     <col min="3" max="3" width="117" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3906,7 +3948,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="2" ht="57" customHeight="1" spans="1:3">
+    <row r="2" ht="43" customHeight="1" spans="1:3">
       <c r="A2" s="1">
         <v>2</v>
       </c>
